--- a/artfynd/A 22931-2019 artfynd.xlsx
+++ b/artfynd/A 22931-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22931-2019 artfynd.xlsx
+++ b/artfynd/A 22931-2019 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117440139</v>
+        <v>117440140</v>
       </c>
       <c r="B4" t="n">
-        <v>57303</v>
+        <v>57306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,25 +931,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117440140</v>
+        <v>117440166</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
+        <v>57715</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,25 +1059,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,15 +1085,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1138,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117440166</v>
+        <v>117440139</v>
       </c>
       <c r="B6" t="n">
-        <v>57715</v>
+        <v>57303</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,21 +1187,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1213,11 +1209,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 22931-2019 artfynd.xlsx
+++ b/artfynd/A 22931-2019 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117440140</v>
+        <v>117440139</v>
       </c>
       <c r="B4" t="n">
-        <v>57306</v>
+        <v>57304</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,25 +931,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117440166</v>
+        <v>117440140</v>
       </c>
       <c r="B5" t="n">
-        <v>57715</v>
+        <v>57307</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,25 +1059,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,11 +1085,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1134,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117440139</v>
+        <v>117440166</v>
       </c>
       <c r="B6" t="n">
-        <v>57303</v>
+        <v>57716</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,21 +1191,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1209,15 +1213,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 22931-2019 artfynd.xlsx
+++ b/artfynd/A 22931-2019 artfynd.xlsx
@@ -922,11 +922,11 @@
         <v>117440139</v>
       </c>
       <c r="B4" t="n">
-        <v>57304</v>
+        <v>57381</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1050,11 +1050,11 @@
         <v>117440140</v>
       </c>
       <c r="B5" t="n">
-        <v>57307</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1178,11 +1178,11 @@
         <v>117440166</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>57793</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/artfynd/A 22931-2019 artfynd.xlsx
+++ b/artfynd/A 22931-2019 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>117440139</v>
       </c>
       <c r="B4" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>117440140</v>
       </c>
       <c r="B5" t="n">
-        <v>57384</v>
+        <v>57388</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>117440166</v>
       </c>
       <c r="B6" t="n">
-        <v>57793</v>
+        <v>57797</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 22931-2019 artfynd.xlsx
+++ b/artfynd/A 22931-2019 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>117440139</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>117440140</v>
       </c>
       <c r="B5" t="n">
-        <v>57393</v>
+        <v>57398</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>117440166</v>
       </c>
       <c r="B6" t="n">
-        <v>57803</v>
+        <v>57808</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 22931-2019 artfynd.xlsx
+++ b/artfynd/A 22931-2019 artfynd.xlsx
@@ -937,11 +937,6 @@
       <c r="E4" t="n">
         <v>100049</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1065,11 +1060,6 @@
       <c r="E5" t="n">
         <v>102977</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Gröngöling</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picus viridis</t>
@@ -1192,11 +1182,6 @@
       </c>
       <c r="E6" t="n">
         <v>103001</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 22931-2019 artfynd.xlsx
+++ b/artfynd/A 22931-2019 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>117440139</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,6 +936,11 @@
       </c>
       <c r="E4" t="n">
         <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1045,7 +1050,7 @@
         <v>117440140</v>
       </c>
       <c r="B5" t="n">
-        <v>57398</v>
+        <v>57402</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,6 +1064,11 @@
       </c>
       <c r="E5" t="n">
         <v>102977</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1168,7 +1178,7 @@
         <v>117440166</v>
       </c>
       <c r="B6" t="n">
-        <v>57808</v>
+        <v>57812</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1182,6 +1192,11 @@
       </c>
       <c r="E6" t="n">
         <v>103001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 22931-2019 artfynd.xlsx
+++ b/artfynd/A 22931-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,131 +1297,6 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>118258494</v>
-      </c>
-      <c r="B7" t="n">
-        <v>106371</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>245</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Campanula cervicaria</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Bånghagen, Born, Nora, Vstm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>500545</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6601828</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Camilla Pettersson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Camilla Pettersson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
